--- a/scripts/fixtures/change-import.xlsx
+++ b/scripts/fixtures/change-import.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>变更类型</t>
+          <t>异动对象</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -440,6 +440,11 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>原因</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>异动类型</t>
         </is>
       </c>
     </row>
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>[IT] 联调批量异动</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>转专业</t>
         </is>
       </c>
     </row>
